--- a/logs/massive_topology_search/experiments_summary.xlsx
+++ b/logs/massive_topology_search/experiments_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/massive_topology_search/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_6E7111A8D3A0D5D94CAB1AD04B5ED87656CAE807" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_335532B6D320D78D948B17D04B5ED87656CABF9F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5580" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2372" uniqueCount="258">
   <si>
     <t>date</t>
   </si>
@@ -786,6 +786,15 @@
   <si>
     <t>03-01_04-07-53_multihead_spsa_compact_f5_w5_h5_effsu2_full_r8.pkl</t>
   </si>
+  <si>
+    <t>03-02_02-42-04_multihead_spsa_compact_f5_w5_h5_effsu2_full_r8.pkl</t>
+  </si>
+  <si>
+    <t>03-03_01-19-26_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r2.pkl</t>
+  </si>
+  <si>
+    <t>[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}]</t>
+  </si>
 </sst>
 </file>
 
@@ -1152,7 +1161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BW114"/>
+  <dimension ref="A1:BW116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:75" x14ac:dyDescent="0.3">
@@ -26658,6 +26667,454 @@
         <v>-0.29988828543455243</v>
       </c>
     </row>
+    <row r="115" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
+        <v>46083.112546296303</v>
+      </c>
+      <c r="B115" t="s">
+        <v>255</v>
+      </c>
+      <c r="C115">
+        <v>3</v>
+      </c>
+      <c r="D115" t="s">
+        <v>76</v>
+      </c>
+      <c r="E115" t="s">
+        <v>77</v>
+      </c>
+      <c r="F115">
+        <v>16590</v>
+      </c>
+      <c r="G115">
+        <v>4.5</v>
+      </c>
+      <c r="H115" t="s">
+        <v>170</v>
+      </c>
+      <c r="I115" t="s">
+        <v>79</v>
+      </c>
+      <c r="J115">
+        <v>5</v>
+      </c>
+      <c r="K115">
+        <v>5</v>
+      </c>
+      <c r="L115" t="s">
+        <v>80</v>
+      </c>
+      <c r="M115" t="s">
+        <v>81</v>
+      </c>
+      <c r="N115" t="s">
+        <v>82</v>
+      </c>
+      <c r="O115" t="s">
+        <v>82</v>
+      </c>
+      <c r="P115" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>236</v>
+      </c>
+      <c r="R115">
+        <v>4</v>
+      </c>
+      <c r="S115" t="s">
+        <v>85</v>
+      </c>
+      <c r="T115" t="s">
+        <v>86</v>
+      </c>
+      <c r="U115" t="s">
+        <v>87</v>
+      </c>
+      <c r="V115" t="s">
+        <v>237</v>
+      </c>
+      <c r="W115" t="s">
+        <v>173</v>
+      </c>
+      <c r="X115" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z115">
+        <v>4000</v>
+      </c>
+      <c r="AA115">
+        <v>4000</v>
+      </c>
+      <c r="AC115">
+        <v>512</v>
+      </c>
+      <c r="AD115" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE115">
+        <v>0.1</v>
+      </c>
+      <c r="AF115">
+        <v>440</v>
+      </c>
+      <c r="AG115">
+        <v>320</v>
+      </c>
+      <c r="AH115">
+        <v>120</v>
+      </c>
+      <c r="AI115">
+        <v>9.5111517238954488E-2</v>
+      </c>
+      <c r="AJ115">
+        <v>21.706679439530909</v>
+      </c>
+      <c r="AK115">
+        <v>0.71007696714144486</v>
+      </c>
+      <c r="AL115">
+        <v>0.13777218883326059</v>
+      </c>
+      <c r="AM115">
+        <v>35.893629939937632</v>
+      </c>
+      <c r="AN115">
+        <v>0.63361233190299326</v>
+      </c>
+      <c r="AO115">
+        <v>35.893629939937632</v>
+      </c>
+      <c r="AP115">
+        <v>35.893629939937632</v>
+      </c>
+      <c r="AQ115">
+        <v>0.63361233190299326</v>
+      </c>
+      <c r="AR115">
+        <v>105.5871357883788</v>
+      </c>
+      <c r="AS115">
+        <v>4.3215620281502581E-2</v>
+      </c>
+      <c r="AT115">
+        <v>0.8</v>
+      </c>
+      <c r="AU115" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV115">
+        <v>6.4836666614307592E-2</v>
+      </c>
+      <c r="AW115">
+        <v>0.52920196925859919</v>
+      </c>
+      <c r="AX115">
+        <v>6.4836666614307592E-2</v>
+      </c>
+      <c r="AY115">
+        <v>6.4836666614307592E-2</v>
+      </c>
+      <c r="AZ115">
+        <v>0.52920196925859919</v>
+      </c>
+      <c r="BA115">
+        <v>9.6276211969363631E-2</v>
+      </c>
+      <c r="BB115">
+        <v>0.30091021995236578</v>
+      </c>
+      <c r="BC115">
+        <v>0.1093327358302809</v>
+      </c>
+      <c r="BD115">
+        <v>0.62118542185364456</v>
+      </c>
+      <c r="BE115">
+        <v>0.1093327358302809</v>
+      </c>
+      <c r="BF115">
+        <v>0.1093327358302809</v>
+      </c>
+      <c r="BG115">
+        <v>0.62118542185364456</v>
+      </c>
+      <c r="BH115">
+        <v>0.33048954534042052</v>
+      </c>
+      <c r="BI115">
+        <v>-0.14507568798290599</v>
+      </c>
+      <c r="BJ115">
+        <v>5.1795564175187443E-2</v>
+      </c>
+      <c r="BK115">
+        <v>0.79205719287223342</v>
+      </c>
+      <c r="BL115">
+        <v>5.1795564175187443E-2</v>
+      </c>
+      <c r="BM115">
+        <v>5.1795564175187443E-2</v>
+      </c>
+      <c r="BN115">
+        <v>0.79205719287223342</v>
+      </c>
+      <c r="BO115">
+        <v>0.19495014239808961</v>
+      </c>
+      <c r="BP115">
+        <v>0.21733684137305981</v>
+      </c>
+      <c r="BQ115">
+        <v>143.348554793131</v>
+      </c>
+      <c r="BR115">
+        <v>0.59200474362749489</v>
+      </c>
+      <c r="BS115">
+        <v>143.348554793131</v>
+      </c>
+      <c r="BT115">
+        <v>143.348554793131</v>
+      </c>
+      <c r="BU115">
+        <v>0.59200474362749489</v>
+      </c>
+      <c r="BV115">
+        <v>421.72682725380753</v>
+      </c>
+      <c r="BW115">
+        <v>-0.2003088922165073</v>
+      </c>
+    </row>
+    <row r="116" spans="1:75" x14ac:dyDescent="0.3">
+      <c r="A116" s="2">
+        <v>46084.055162037039</v>
+      </c>
+      <c r="B116" t="s">
+        <v>256</v>
+      </c>
+      <c r="C116">
+        <v>1</v>
+      </c>
+      <c r="D116" t="s">
+        <v>76</v>
+      </c>
+      <c r="E116" t="s">
+        <v>77</v>
+      </c>
+      <c r="F116">
+        <v>16590</v>
+      </c>
+      <c r="G116">
+        <v>4.5</v>
+      </c>
+      <c r="H116" t="s">
+        <v>170</v>
+      </c>
+      <c r="I116" t="s">
+        <v>79</v>
+      </c>
+      <c r="J116">
+        <v>5</v>
+      </c>
+      <c r="K116">
+        <v>5</v>
+      </c>
+      <c r="L116" t="s">
+        <v>80</v>
+      </c>
+      <c r="M116" t="s">
+        <v>81</v>
+      </c>
+      <c r="N116" t="s">
+        <v>82</v>
+      </c>
+      <c r="O116" t="s">
+        <v>82</v>
+      </c>
+      <c r="P116" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>257</v>
+      </c>
+      <c r="R116">
+        <v>4</v>
+      </c>
+      <c r="S116" t="s">
+        <v>85</v>
+      </c>
+      <c r="T116" t="s">
+        <v>86</v>
+      </c>
+      <c r="U116" t="s">
+        <v>110</v>
+      </c>
+      <c r="V116" t="s">
+        <v>172</v>
+      </c>
+      <c r="W116" t="s">
+        <v>173</v>
+      </c>
+      <c r="X116" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y116" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z116">
+        <v>4000</v>
+      </c>
+      <c r="AA116">
+        <v>4000</v>
+      </c>
+      <c r="AC116">
+        <v>512</v>
+      </c>
+      <c r="AD116" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE116">
+        <v>0.1</v>
+      </c>
+      <c r="AF116">
+        <v>200</v>
+      </c>
+      <c r="AG116">
+        <v>80</v>
+      </c>
+      <c r="AH116">
+        <v>120</v>
+      </c>
+      <c r="AI116">
+        <v>7.2955293197742244E-2</v>
+      </c>
+      <c r="AJ116">
+        <v>12.689402052466789</v>
+      </c>
+      <c r="AK116">
+        <v>0.78974256903254514</v>
+      </c>
+      <c r="AL116">
+        <v>-5.0314965514804633E-2</v>
+      </c>
+      <c r="AM116">
+        <v>14.796927003355609</v>
+      </c>
+      <c r="AN116">
+        <v>0.7960035020959586</v>
+      </c>
+      <c r="AO116">
+        <v>14.796927003355609</v>
+      </c>
+      <c r="AP116">
+        <v>14.796927003355609</v>
+      </c>
+      <c r="AQ116">
+        <v>0.7960035020959586</v>
+      </c>
+      <c r="AR116">
+        <v>228.4102505292411</v>
+      </c>
+      <c r="AS116">
+        <v>-6.1352646996310767E-2</v>
+      </c>
+      <c r="AT116">
+        <v>0.8</v>
+      </c>
+      <c r="AU116" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV116">
+        <v>2.1566851671586621E-2</v>
+      </c>
+      <c r="AW116">
+        <v>0.84339677181932338</v>
+      </c>
+      <c r="AX116">
+        <v>2.1566851671586621E-2</v>
+      </c>
+      <c r="AY116">
+        <v>2.1566851671586621E-2</v>
+      </c>
+      <c r="AZ116">
+        <v>0.84339677181932338</v>
+      </c>
+      <c r="BA116">
+        <v>5.4442523907353178E-2</v>
+      </c>
+      <c r="BB116">
+        <v>0.60467688450662282</v>
+      </c>
+      <c r="BC116">
+        <v>8.860763825186993E-2</v>
+      </c>
+      <c r="BD116">
+        <v>0.69299345845482319</v>
+      </c>
+      <c r="BE116">
+        <v>8.860763825186993E-2</v>
+      </c>
+      <c r="BF116">
+        <v>8.860763825186993E-2</v>
+      </c>
+      <c r="BG116">
+        <v>0.69299345845482319</v>
+      </c>
+      <c r="BH116">
+        <v>0.25936558978461888</v>
+      </c>
+      <c r="BI116">
+        <v>0.10135362722050111</v>
+      </c>
+      <c r="BJ116">
+        <v>4.5921886495760761E-2</v>
+      </c>
+      <c r="BK116">
+        <v>0.81563815089969305</v>
+      </c>
+      <c r="BL116">
+        <v>4.5921886495760761E-2</v>
+      </c>
+      <c r="BM116">
+        <v>4.5921886495760761E-2</v>
+      </c>
+      <c r="BN116">
+        <v>0.81563815089969305</v>
+      </c>
+      <c r="BO116">
+        <v>8.7728105308024246E-2</v>
+      </c>
+      <c r="BP116">
+        <v>0.64779940575509976</v>
+      </c>
+      <c r="BQ116">
+        <v>59.031611637003209</v>
+      </c>
+      <c r="BR116">
+        <v>0.83198562720999703</v>
+      </c>
+      <c r="BS116">
+        <v>59.031611637003209</v>
+      </c>
+      <c r="BT116">
+        <v>59.031611637003209</v>
+      </c>
+      <c r="BU116">
+        <v>0.83198562720999703</v>
+      </c>
+      <c r="BV116">
+        <v>913.23946589796401</v>
+      </c>
+      <c r="BW116">
+        <v>-1.5992405054674721</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/logs/massive_topology_search/experiments_summary.xlsx
+++ b/logs/massive_topology_search/experiments_summary.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW117"/>
+  <dimension ref="A1:BW120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31517,6 +31517,801 @@
       </c>
       <c r="BW117" t="n">
         <v>0.00275655493797955</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46084.57675925926</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>03-03_13-50-32_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r2.pkl</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>3</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G118" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>[['wv', 'rarad'], ['sv', 'rarad'], ['yr', 'rarad'], ['ya', 'yr']]</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>5</v>
+      </c>
+      <c r="K118" t="n">
+        <v>5</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 2, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}]</t>
+        </is>
+      </c>
+      <c r="R118" t="n">
+        <v>4</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>compact</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>[0, 1, -1]</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z118" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB118" t="inlineStr"/>
+      <c r="AC118" t="n">
+        <v>512</v>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>200</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.08105220573636279</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>14.22849995965816</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.7774650161262389</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>-0.3388975246539947</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>15.86200773838604</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.7844286187848384</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>15.86200773838604</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>15.86200773838604</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.7844286187848384</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>121.2011399753766</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.08121096154663379</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.0283019685462523</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.7944911150823982</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.0283019685462523</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.0283019685462523</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.7944911150823982</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.08737544162379303</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.3655413209882012</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.08535310008314037</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.7042697380986647</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.08535310008314037</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.08535310008314037</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.7042697380986647</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.2534592977581041</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.1218176676146474</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.04506303625940902</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.8190861629426796</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.04506303625940902</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.04506303625940902</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.8190861629426796</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.357276102058979</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>-0.434350542655165</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>63.28931284865537</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.8198674590156094</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>63.28931284865537</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>63.28931284865537</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.8198674590156094</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>484.1064490600652</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>-0.3778522921342271</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46084.9068287037</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>03-03_21-45-50_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r3.pkl</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G119" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>[['wv', 'rarad'], ['sv', 'rarad'], ['yr', 'rarad'], ['ya', 'yr']]</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>5</v>
+      </c>
+      <c r="K119" t="n">
+        <v>5</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}]</t>
+        </is>
+      </c>
+      <c r="R119" t="n">
+        <v>4</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>compact</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>[0, 1, -1]</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z119" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB119" t="inlineStr"/>
+      <c r="AC119" t="n">
+        <v>512</v>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>240</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>120</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.106008494446163</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>33.83893112988854</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.6662154986094835</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.05379237680349236</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>35.08238745519761</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.6848060644280534</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>35.08238745519761</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>35.08238745519761</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.6848060644280534</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>114.439596298278</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.6172042429998836</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.03832012905145635</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.7217463167484792</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.03832012905145635</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.03832012905145635</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7217463167484792</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.1118626898969249</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.1877322375285925</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.08000239142595358</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7228088007807025</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.08000239142595358</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.08000239142595358</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.7228088007807025</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.3205165810134426</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.1105214966357024</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.07634032756076768</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.6935177314345414</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.07634032756076768</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.07634032756076768</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.6935177314345414</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.8087060518111804</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>-2.246699002757245</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>140.134886972753</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6011514087484886</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>140.134886972753</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>140.134886972753</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6011514087484886</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>456.5172998703921</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>-0.2993287101352031</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46085.22273148148</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>03-04_05-20-44_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r3.pkl</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>2</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G120" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>[['wv', 'rarad'], ['sv', 'rarad'], ['yr', 'rarad'], ['ya', 'yr']]</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>5</v>
+      </c>
+      <c r="K120" t="n">
+        <v>5</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}]</t>
+        </is>
+      </c>
+      <c r="R120" t="n">
+        <v>4</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>compact</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>[0, 1, -1]</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z120" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB120" t="inlineStr"/>
+      <c r="AC120" t="n">
+        <v>512</v>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>240</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>120</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.08632604452620456</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>14.14679972273368</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.7226253060179254</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.07581434566459494</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>25.02622838431372</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.7329176143886131</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>25.02622838431372</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>25.02622838431372</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.7329176143886131</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>120.5007286916416</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.04680918733523903</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.04360446843827038</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.6833751803684935</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.04360446843827038</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.04360446843827038</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.6833751803684935</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.152507687958842</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>-0.1074030006981048</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.1019325895310629</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.6468253482423081</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.1019325895310629</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.1019325895310629</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.6468253482423081</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.3016001542865092</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.04498011823533599</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.02842290201774232</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.885891038616814</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.02842290201774232</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.02842290201774232</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.885891038616814</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.0722380551041809</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.7099870577911451</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>99.93095357726796</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.7155788903268383</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>99.93095357726796</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>99.93095357726796</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.7155788903268383</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>481.4765688692148</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>-0.3703671895167404</v>
       </c>
     </row>
   </sheetData>

--- a/logs/massive_topology_search/experiments_summary.xlsx
+++ b/logs/massive_topology_search/experiments_summary.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW120"/>
+  <dimension ref="A1:BW121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32312,6 +32312,271 @@
       </c>
       <c r="BW120" t="n">
         <v>-0.3703671895167404</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46085.56421296296</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>03-04_13-32-28_multihead_spsa_compact_f5_w5_h5_effsu2_lin_r3.pkl</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>3</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G121" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>[['wv', 'rarad'], ['sv', 'rarad'], ['yr', 'rarad'], ['ya', 'yr']]</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>['Surge Velocity', 'Sway Velocity', 'Yaw Rate', 'Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>5</v>
+      </c>
+      <c r="K121" t="n">
+        <v>5</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>motion</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>[{'features': ['wv', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['sv', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['yr', 'rarad'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}, {'features': ['ya', 'yr'], 'output_dim': 1, 'reps': 3, 'encoding': 'compact', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, -1]}]</t>
+        </is>
+      </c>
+      <c r="R121" t="n">
+        <v>4</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>compact</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>[0, 1, -1]</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z121" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB121" t="inlineStr"/>
+      <c r="AC121" t="n">
+        <v>512</v>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>[0.05, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>240</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>120</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.1029099622824071</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>26.93196602965658</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.6844397084874109</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.08629365791592702</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>28.81214679766711</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.6773459445860944</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>28.81214679766711</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>28.81214679766711</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.6773459445860944</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>112.7319246644321</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.01259564723973675</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.03494155098943168</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.7462791618401223</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.03494155098943168</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.03494155098943168</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.7462791618401223</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.1223043357798201</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.1119123878036022</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.1088797158354875</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.6227550393786823</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.1088797158354875</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.1088797158354875</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.6227550393786823</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.2670718603324239</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.07465304569311626</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.0827655573345633</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.6677224662051686</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.0827655573345633</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.0827655573345633</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.6677224662051686</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2128379709887903</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.1455228675356532</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>115.0220003665092</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.6726271109204025</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>115.0220003665092</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>115.0220003665092</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.6726271109204025</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>450.3254844906265</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>-0.2817057120734205</v>
       </c>
     </row>
   </sheetData>
